--- a/artfynd/A 20977-2025 artfynd.xlsx
+++ b/artfynd/A 20977-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>2907222</v>
       </c>
       <c r="B2" t="n">
-        <v>96369</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98608</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>457326.6288672481</v>
+        <v>457327</v>
       </c>
       <c r="R2" t="n">
-        <v>6491994.352231356</v>
+        <v>6491994</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -748,19 +743,9 @@
           <t>1984-07-16</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1984-07-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -910,12 +895,7 @@
         <v>237313</v>
       </c>
       <c r="B4" t="n">
-        <v>104642</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107050</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -947,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>457326.6288672481</v>
+        <v>457327</v>
       </c>
       <c r="R4" t="n">
-        <v>6491994.352231356</v>
+        <v>6491994</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -980,19 +960,9 @@
           <t>1984-07-16</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1984-07-16</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 20977-2025 artfynd.xlsx
+++ b/artfynd/A 20977-2025 artfynd.xlsx
@@ -779,12 +779,7 @@
         <v>4006400</v>
       </c>
       <c r="B3" t="n">
-        <v>99565</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101832</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>457326.6288672481</v>
+        <v>457327</v>
       </c>
       <c r="R3" t="n">
-        <v>6491994.352231356</v>
+        <v>6491994</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -849,19 +844,9 @@
           <t>1984-07-16</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1984-07-16</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 20977-2025 artfynd.xlsx
+++ b/artfynd/A 20977-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>2907222</v>
       </c>
       <c r="B2" t="n">
-        <v>98608</v>
+        <v>98616</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>4006400</v>
       </c>
       <c r="B3" t="n">
-        <v>101832</v>
+        <v>101840</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>237313</v>
       </c>
       <c r="B4" t="n">
-        <v>107050</v>
+        <v>107064</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 20977-2025 artfynd.xlsx
+++ b/artfynd/A 20977-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>2907222</v>
       </c>
       <c r="B2" t="n">
-        <v>98616</v>
+        <v>98622</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>4006400</v>
       </c>
       <c r="B3" t="n">
-        <v>101840</v>
+        <v>101848</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>237313</v>
       </c>
       <c r="B4" t="n">
-        <v>107064</v>
+        <v>107073</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 20977-2025 artfynd.xlsx
+++ b/artfynd/A 20977-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>2907222</v>
       </c>
       <c r="B2" t="n">
-        <v>98622</v>
+        <v>98625</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>4006400</v>
       </c>
       <c r="B3" t="n">
-        <v>101848</v>
+        <v>101853</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>237313</v>
       </c>
       <c r="B4" t="n">
-        <v>107073</v>
+        <v>107085</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 20977-2025 artfynd.xlsx
+++ b/artfynd/A 20977-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>2907222</v>
       </c>
       <c r="B2" t="n">
-        <v>98625</v>
+        <v>98628</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>4006400</v>
       </c>
       <c r="B3" t="n">
-        <v>101853</v>
+        <v>101859</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>237313</v>
       </c>
       <c r="B4" t="n">
-        <v>107085</v>
+        <v>107094</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 20977-2025 artfynd.xlsx
+++ b/artfynd/A 20977-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>2907222</v>
       </c>
       <c r="B2" t="n">
-        <v>98628</v>
+        <v>98629</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>4006400</v>
       </c>
       <c r="B3" t="n">
-        <v>101859</v>
+        <v>101860</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>237313</v>
       </c>
       <c r="B4" t="n">
-        <v>107094</v>
+        <v>107099</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 20977-2025 artfynd.xlsx
+++ b/artfynd/A 20977-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>2907222</v>
       </c>
       <c r="B2" t="n">
-        <v>98629</v>
+        <v>98656</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>4006400</v>
       </c>
       <c r="B3" t="n">
-        <v>101860</v>
+        <v>101887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>237313</v>
       </c>
       <c r="B4" t="n">
-        <v>107099</v>
+        <v>107127</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 20977-2025 artfynd.xlsx
+++ b/artfynd/A 20977-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>2907222</v>
       </c>
       <c r="B2" t="n">
-        <v>98656</v>
+        <v>98662</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>4006400</v>
       </c>
       <c r="B3" t="n">
-        <v>101887</v>
+        <v>101893</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>237313</v>
       </c>
       <c r="B4" t="n">
-        <v>107127</v>
+        <v>107133</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 20977-2025 artfynd.xlsx
+++ b/artfynd/A 20977-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>2907222</v>
       </c>
       <c r="B2" t="n">
-        <v>98662</v>
+        <v>98669</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>4006400</v>
       </c>
       <c r="B3" t="n">
-        <v>101893</v>
+        <v>101900</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>237313</v>
       </c>
       <c r="B4" t="n">
-        <v>107133</v>
+        <v>107140</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 20977-2025 artfynd.xlsx
+++ b/artfynd/A 20977-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>2907222</v>
       </c>
       <c r="B2" t="n">
-        <v>98669</v>
+        <v>98673</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>4006400</v>
       </c>
       <c r="B3" t="n">
-        <v>101900</v>
+        <v>101904</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>237313</v>
       </c>
       <c r="B4" t="n">
-        <v>107140</v>
+        <v>107144</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 20977-2025 artfynd.xlsx
+++ b/artfynd/A 20977-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>2907222</v>
       </c>
       <c r="B2" t="n">
-        <v>98673</v>
+        <v>98680</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>4006400</v>
       </c>
       <c r="B3" t="n">
-        <v>101904</v>
+        <v>101911</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>237313</v>
       </c>
       <c r="B4" t="n">
-        <v>107144</v>
+        <v>107152</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
